--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nivis\my_projects\projects_myTimetable\college_Timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AB044F-8555-4030-BA69-AD30790F6A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056DE4AB-E131-4F6D-8BD2-E261CB432264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8610" yWindow="3180" windowWidth="17925" windowHeight="10305" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="2295" windowWidth="20670" windowHeight="9120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="s2" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="16">
   <si>
     <t>week_day</t>
   </si>
@@ -75,198 +75,6 @@
   </si>
   <si>
     <t>friday</t>
-  </si>
-  <si>
-    <t>mon_s1[2]</t>
-  </si>
-  <si>
-    <t>mon_s2[]</t>
-  </si>
-  <si>
-    <t>mon_s3[]</t>
-  </si>
-  <si>
-    <t>mon_s4[]</t>
-  </si>
-  <si>
-    <t>mon_s5[]</t>
-  </si>
-  <si>
-    <t>mon_s6[]</t>
-  </si>
-  <si>
-    <t>mon_sx[]</t>
-  </si>
-  <si>
-    <t>tue_s1[2]</t>
-  </si>
-  <si>
-    <t>tue_s2[]</t>
-  </si>
-  <si>
-    <t>tue_s3[]</t>
-  </si>
-  <si>
-    <t>tue_s4[]</t>
-  </si>
-  <si>
-    <t>tue_s5[]</t>
-  </si>
-  <si>
-    <t>tue_s6[]</t>
-  </si>
-  <si>
-    <t>tue_sx[]</t>
-  </si>
-  <si>
-    <t>wed_s1[2]</t>
-  </si>
-  <si>
-    <t>wed_s2[]</t>
-  </si>
-  <si>
-    <t>wed_s3[]</t>
-  </si>
-  <si>
-    <t>wed_s4[]</t>
-  </si>
-  <si>
-    <t>wed_s5[]</t>
-  </si>
-  <si>
-    <t>wed_s6[]</t>
-  </si>
-  <si>
-    <t>wed_sx[]</t>
-  </si>
-  <si>
-    <t>thu_s1[2]</t>
-  </si>
-  <si>
-    <t>thu_s2[]</t>
-  </si>
-  <si>
-    <t>thu_s3[]</t>
-  </si>
-  <si>
-    <t>thu_s4[]</t>
-  </si>
-  <si>
-    <t>thu_s5[]</t>
-  </si>
-  <si>
-    <t>thu_s6[]</t>
-  </si>
-  <si>
-    <t>thu_sx[]</t>
-  </si>
-  <si>
-    <t>fri_s1[2]</t>
-  </si>
-  <si>
-    <t>fri_s2[]</t>
-  </si>
-  <si>
-    <t>fri_s3[]</t>
-  </si>
-  <si>
-    <t>fri_s4[]</t>
-  </si>
-  <si>
-    <t>fri_s5[]</t>
-  </si>
-  <si>
-    <t>fri_s6[]</t>
-  </si>
-  <si>
-    <t>fri_sx[]</t>
-  </si>
-  <si>
-    <t>mon_s1[3]</t>
-  </si>
-  <si>
-    <t>tue_s1[3]</t>
-  </si>
-  <si>
-    <t>wed_s1[3]</t>
-  </si>
-  <si>
-    <t>thu_s13[]</t>
-  </si>
-  <si>
-    <t>fri_s1[3]</t>
-  </si>
-  <si>
-    <t>mon_s1[4]</t>
-  </si>
-  <si>
-    <t>tue_s1[4]</t>
-  </si>
-  <si>
-    <t>wed_s1[4]</t>
-  </si>
-  <si>
-    <t>thu_s1[4]</t>
-  </si>
-  <si>
-    <t>fri_s1[4]</t>
-  </si>
-  <si>
-    <t>mon_s1[5]</t>
-  </si>
-  <si>
-    <t>tue_s1[5]</t>
-  </si>
-  <si>
-    <t>wed_s1[5]</t>
-  </si>
-  <si>
-    <t>thu_s1[5]</t>
-  </si>
-  <si>
-    <t>fri_s1[5]</t>
-  </si>
-  <si>
-    <t>mon_s1[6]</t>
-  </si>
-  <si>
-    <t>tue_s1[6]</t>
-  </si>
-  <si>
-    <t>wed_s1[6]</t>
-  </si>
-  <si>
-    <t>thu_s1[6]</t>
-  </si>
-  <si>
-    <t>fri_s1[6]</t>
-  </si>
-  <si>
-    <t>mon_s1[7]</t>
-  </si>
-  <si>
-    <t>tue_s1[7]</t>
-  </si>
-  <si>
-    <t>wed_s1[7]</t>
-  </si>
-  <si>
-    <t>thu_s1[7]</t>
-  </si>
-  <si>
-    <t>fri_s1[7]</t>
-  </si>
-  <si>
-    <t>tue_s1[8]</t>
-  </si>
-  <si>
-    <t>wed_s1[8]</t>
-  </si>
-  <si>
-    <t>thu_s1[8]</t>
-  </si>
-  <si>
-    <t>fri_s1[8]</t>
   </si>
 </sst>
 </file>
@@ -661,25 +469,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -687,25 +495,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -713,25 +521,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -739,25 +547,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -765,25 +573,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -827,25 +635,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -853,25 +661,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -879,25 +687,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -905,25 +713,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -931,25 +739,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -993,25 +801,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1019,25 +827,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1045,25 +853,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1071,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1097,25 +905,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1159,25 +967,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,25 +993,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,25 +1019,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,25 +1045,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,25 +1071,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1325,25 +1133,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1351,25 +1159,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1377,25 +1185,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1403,25 +1211,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1429,25 +1237,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1492,25 +1300,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1518,25 +1326,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1544,25 +1352,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1570,25 +1378,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1596,25 +1404,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1658,25 +1466,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1684,25 +1492,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1710,25 +1518,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1736,25 +1544,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1762,25 +1570,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
